--- a/artifacts_progressao/planilha_progressao.xlsx
+++ b/artifacts_progressao/planilha_progressao.xlsx
@@ -25,11 +25,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +47,10 @@
     </font>
     <font>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="7">
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -125,6 +130,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +558,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>79f176c</t>
+          <t>fe81cab</t>
         </is>
       </c>
     </row>
@@ -560,7 +570,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T16:54:37-03:00</t>
+          <t>2026-09-28T17:43:09-03:00</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD9"/>
+  <dimension ref="A1:BG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2759,7 +2769,10 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
-    <col width="46" customWidth="1" min="56" max="56"/>
+    <col width="40" customWidth="1" min="56" max="56"/>
+    <col width="46" customWidth="1" min="57" max="57"/>
+    <col width="60" customWidth="1" min="58" max="58"/>
+    <col width="46" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3043,6 +3056,21 @@
           <t>o que o jogador deve sentir</t>
         </is>
       </c>
+      <c r="BE1" s="8" t="inlineStr">
+        <is>
+          <t>o jogador aprende (B1)</t>
+        </is>
+      </c>
+      <c r="BF1" s="8" t="inlineStr">
+        <is>
+          <t>como é ensinado (tutorial contextual)</t>
+        </is>
+      </c>
+      <c r="BG1" s="8" t="inlineStr">
+        <is>
+          <t>sinal de que aprendeu</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3184,6 +3212,21 @@
           <t>curiosidade: o que vai sair do ovo</t>
         </is>
       </c>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>o pet é dele; o tempo do pet anda com o app aberto (fechar = pausa)</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>Bit, ao chocar: 'é seu; enquanto a janela estiver aberta, ele vive'. Uma frase por tela, some ao tocar</t>
+        </is>
+      </c>
+      <c r="BG2" s="2" t="inlineStr">
+        <is>
+          <t>tocou no ovo e escolheu a velocidade do tempo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3325,6 +3368,21 @@
           <t>atender rápido mudou quem ele é</t>
         </is>
       </c>
+      <c r="BE3" s="2" t="inlineStr">
+        <is>
+          <t>chamados e janela de 15 min (fome, higiene, carinho); atender rápido importa</t>
+        </is>
+      </c>
+      <c r="BF3" s="2" t="inlineStr">
+        <is>
+          <t>no primeiro chamado: o tempo cai para 1x, Bit aponta o balão e o botão certo; na revelação: 'você atendeu X de Y chamados'</t>
+        </is>
+      </c>
+      <c r="BG3" s="2" t="inlineStr">
+        <is>
+          <t>atendeu 3 chamados dentro da janela</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3563,6 +3621,21 @@
           <t>preciso treinar para vencer o primeiro rival</t>
         </is>
       </c>
+      <c r="BE4" s="2" t="inlineStr">
+        <is>
+          <t>treino por botão (sem forçar); o primeiro rival pede treino</t>
+        </is>
+      </c>
+      <c r="BF4" s="2" t="inlineStr">
+        <is>
+          <t>Bit leva à sala de treino no primeiro minuto do Rookie; no primeiro Desafiar perdido, 'faltou força: treine e volte'</t>
+        </is>
+      </c>
+      <c r="BG4" s="2" t="inlineStr">
+        <is>
+          <t>treinou 3 sessões e venceu o Brutamontes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3704,6 +3777,21 @@
           <t>o jeito que ensinei virou a linha dele</t>
         </is>
       </c>
+      <c r="BE5" s="2" t="inlineStr">
+        <is>
+          <t>ensinar: elogiar e repreender o que ele acabou de fazer; necessidade × vontade; a primeira recusa</t>
+        </is>
+      </c>
+      <c r="BF5" s="2" t="inlineStr">
+        <is>
+          <t>na primeira ação espontânea: Bit mostra Elogiar/Repreender e o 'o que muda'; na primeira recusa, o balão com o porquê</t>
+        </is>
+      </c>
+      <c r="BG5" s="2" t="inlineStr">
+        <is>
+          <t>elogiou ou repreendeu 3 vezes na janela de 2 min</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3942,6 +4030,21 @@
           <t>um rival pede stats, outro pede estilo</t>
         </is>
       </c>
+      <c r="BE6" s="2" t="inlineStr">
+        <is>
+          <t>a linha que o caráter decidiu e a técnica; fadiga, 'Forçar' e o aviso de sobrecarga</t>
+        </is>
+      </c>
+      <c r="BF6" s="2" t="inlineStr">
+        <is>
+          <t>revelação do Champion mostra o eixo que decidiu; na fadiga 40 o pet pede pausa (Bit explica uma vez); no primeiro Forçar, a folha com o custo</t>
+        </is>
+      </c>
+      <c r="BG6" s="2" t="inlineStr">
+        <is>
+          <t>leu o porquê da linha; atendeu uma pausa (ou forçou sabendo o custo)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4083,6 +4186,21 @@
           <t>a forma final veio do caráter e do treino</t>
         </is>
       </c>
+      <c r="BE7" s="2" t="inlineStr">
+        <is>
+          <t>travar/vetar regras de combate; as 10 lutas de treino</t>
+        </is>
+      </c>
+      <c r="BF7" s="2" t="inlineStr">
+        <is>
+          <t>depois da primeira luta, o Resultado mostra a regra nova com Travar/Vetar; o contador 'x de 10' aparece no topo</t>
+        </is>
+      </c>
+      <c r="BG7" s="2" t="inlineStr">
+        <is>
+          <t>travou ou vetou uma regra; completou as 10 lutas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4321,6 +4439,21 @@
           <t>o chefe exige tudo o que aprendi</t>
         </is>
       </c>
+      <c r="BE8" s="2" t="inlineStr">
+        <is>
+          <t>forma final e passiva; a arena contra outros pets</t>
+        </is>
+      </c>
+      <c r="BF8" s="2" t="inlineStr">
+        <is>
+          <t>o próprio pet explica a passiva na revelação (a partir do adulto ele fala)</t>
+        </is>
+      </c>
+      <c r="BG8" s="2" t="inlineStr">
+        <is>
+          <t>desafiou o chefe</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4468,6 +4601,21 @@
       <c r="BD9" s="2" t="inlineStr">
         <is>
           <t>meu pet é o meu, diferente dos outros</t>
+        </is>
+      </c>
+      <c r="BE9" s="2" t="inlineStr">
+        <is>
+          <t>o que fazer depois: arena, Melhor de 10, cenários; um novo ovo</t>
+        </is>
+      </c>
+      <c r="BF9" s="2" t="inlineStr">
+        <is>
+          <t>o pet sugere o que falta (formas vistas no Catálogo, chefe não vencido)</t>
+        </is>
+      </c>
+      <c r="BG9" s="2" t="inlineStr">
+        <is>
+          <t>voltou ao jogo depois de vencer o chefe</t>
         </is>
       </c>
     </row>
@@ -8171,16 +8319,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -8190,7 +8338,9 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8231,7 +8381,7 @@
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>vida proposta</t>
+          <t>vida proposta (escala E)</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
@@ -8276,7 +8426,17 @@
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>fator de escala proposto (vida proposta / vida hoje)</t>
+          <t>degrau hoje (× do estágio anterior)</t>
+        </is>
+      </c>
+      <c r="R1" s="8" t="inlineStr">
+        <is>
+          <t>degrau proposto</t>
+        </is>
+      </c>
+      <c r="S1" s="8" t="inlineStr">
+        <is>
+          <t>degrau DW1</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8477,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>proposta desta planilha (B2: ~50 / 200 / 600 / 1500)</t>
+          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
@@ -8350,10 +8510,6 @@
         <f>K2/K2</f>
         <v/>
       </c>
-      <c r="Q2" s="9">
-        <f>H2/B2</f>
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8392,7 +8548,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>proposta desta planilha (B2: ~50 / 200 / 600 / 1500)</t>
+          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
@@ -8425,8 +8581,16 @@
         <f>K3/K2</f>
         <v/>
       </c>
-      <c r="Q3" s="9">
-        <f>H3/B3</f>
+      <c r="Q3" s="12">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="R3" s="12">
+        <f>H3/H2</f>
+        <v/>
+      </c>
+      <c r="S3" s="12">
+        <f>K3/K2</f>
         <v/>
       </c>
     </row>
@@ -8467,7 +8631,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>proposta desta planilha (B2: ~50 / 200 / 600 / 1500)</t>
+          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
@@ -8500,8 +8664,16 @@
         <f>K4/K2</f>
         <v/>
       </c>
-      <c r="Q4" s="9">
-        <f>H4/B4</f>
+      <c r="Q4" s="12">
+        <f>B4/B3</f>
+        <v/>
+      </c>
+      <c r="R4" s="12">
+        <f>H4/H3</f>
+        <v/>
+      </c>
+      <c r="S4" s="12">
+        <f>K4/K3</f>
         <v/>
       </c>
     </row>
@@ -8542,7 +8714,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>proposta desta planilha (B2: ~50 / 200 / 600 / 1500)</t>
+          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -8575,498 +8747,1458 @@
         <f>K5/K2</f>
         <v/>
       </c>
-      <c r="Q5" s="9">
-        <f>H5/B5</f>
+      <c r="Q5" s="12">
+        <f>B5/B4</f>
+        <v/>
+      </c>
+      <c r="R5" s="12">
+        <f>H5/H4</f>
+        <v/>
+      </c>
+      <c r="S5" s="12">
+        <f>K5/K4</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>constante absoluta do combate</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>campo</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>fonte</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>tipo</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>como tornar relativa</t>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Desenho (PROPOSTO): perfil × escala</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>dano do golpe rápido</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCombateV2.dano_golpe_rapido</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV2.dano_golpe_rapido</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>dano</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>× mult_perto; relativo se vier da vida (fração de vida neutra)</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>peça</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>regra</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>dano do disparo</t>
+          <t>perfil</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ConfigCombateV2.dano_disparo</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV2.dano_disparo</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>dano</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>idem</t>
+          <t>os pontos do catálogo (espécie + temperamento + caráter + arquétipos, soma zero): o que a pesquisa compara; não muda</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dano do pesado</t>
+          <t>escala E</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ConfigCombateV2.dano_pesado</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>25</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV2.dano_pesado</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>dano</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>idem</t>
+          <t>magnitude do lutador: E = E_estágio × (1 + β × pontos treinados). Vida exibida = vida de hoje sem o mult. de estágio × E</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>dano do parry (V2C)</t>
+          <t>combate</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ConfigCombateV2C.dano_parry</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV2C.dano_parry</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>dano</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>idem</t>
+          <t>cada lutador luta nas próprias unidades (vida e dano de hoje, sem o mult. de estágio); o dano que A causa em B é multiplicado por E_A / E_B. Guts fica absoluto (é ritmo, não magnitude)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>dano da investida</t>
+          <t>invariância</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ConfigCombateV21.dano_investida</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV21.dano_investida</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>dano</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>idem</t>
+          <t>multiplicar E dos dois lados pelo mesmo fator dá E_A/E_B idêntico (mesmo float): a luta é exatamente a mesma. Lutas entre pets do mesmo estágio e sem treino têm razão 1,0 exato: a bateria V21C não muda</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>dano extra do duelista</t>
+          <t>pesquisa</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ConfigCombateV21.dano_extra_duelista</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV21.dano_extra_duelista</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>dano</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>idem</t>
+          <t>a arena da pesquisa fixa E igual nos dois lados (adultos, treino normalizado ao orçamento): a escala não entra lá</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>vida base</t>
+          <t>mult. de estágio de hoje</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ConfigCombateV21C.hp_base</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>75</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV21C.hp_base</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>vida</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>a vida escala; o dano tem de escalar junto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>vida por vigor</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCombateV21C.hp_por_vigor</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV21C.hp_por_vigor</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>vida</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>idem</t>
+          <t>sai do combate na campanha (a escala faz o papel dele); fica só na arena antiga e nas runs de pesquisa</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>custos de guts (golpe 10, pesado 15, disparo e esquiva 20)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCombateV2.custo_*</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV2.custo_*</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>guts</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>guts não precisa escalar: é recurso de ritmo, não magnitude</t>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Treino na escala (B2.5)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>guts máximo, inicial, regen, carregar +25, defender +5</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCombateV21 / V2</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>digilab/config.py &gt; ConfigCombateV21 / V2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>guts</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>idem (fica absoluto)</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>estágio</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>E do estágio</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>β por ponto</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>pontos típicos no fim do estágio</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>E com treino típico</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>ganho em vida exibida por ponto</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>ganho relativo por ponto</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>limiares de guts nas condições (20, 40, 60)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCombateV2.limiares_guts</t>
-        </is>
+          <t>crianca</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>H3</f>
+        <v/>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>0.03</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>digilab/config.py &gt; ConfigCombateV2.limiares_guts</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>guts</t>
-        </is>
+          <t>proposta: 36 pontos → ×2,08 (o treino inteiro da vida pouco mais que dobra a escala)</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>idem</t>
-        </is>
+          <t>experiments/calibrar_progressao.py &gt; ALCANCE['tier1']['crianca']</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="I18" s="16">
+        <f>B18*(1+C18*F18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="9">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>C18/(1+C18*F18)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>multiplicadores de força/mira/guarda (0,7 + 0,03 × stat)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>ConfigCombateV21.mult_base / mult_por_ponto</t>
-        </is>
+          <t>adolescente</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>H4</f>
+        <v/>
       </c>
       <c r="C19" t="n">
         <v>0.03</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>digilab/config.py &gt; ConfigCombateV21.mult_base / mult_por_ponto</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>stat</t>
-        </is>
+          <t>proposta: 36 pontos → ×2,08 (o treino inteiro da vida pouco mais que dobra a escala)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>22</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>dependem do stat de catálogo, que NÃO escala (o perfil fica)</t>
-        </is>
+          <t>experiments/calibrar_progressao.py &gt; ALCANCE['tier2']['adolescente']</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="I19" s="16">
+        <f>B19*(1+C19*F19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="9">
+        <f>B19*C19</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>C19/(1+C19*F19)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>adulto</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="C20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>proposta: 36 pontos → ×2,08 (o treino inteiro da vida pouco mais que dobra a escala)</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>36</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>experiments/calibrar_progressao.py &gt; ALCANCE['tier3']['adulto']</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="I20" s="16">
+        <f>B20*(1+C20*F20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>C20/(1+C20*F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>peso_ponto_combate</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigTreino.peso_ponto_combate</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>na nova base o ponto treinado vai para a escala (β) e para o perfil (proporções, como na arena normalizada); o ×3 absoluto sai da campanha (proposta: o perfil treinado é sempre normalizado ao orçamento)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>NPCs na escala e efeito nas metas (sem run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>portão</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>E do pet sem treino</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>E do pet com treino típico</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>fator do NPC</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>E do NPC</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>razão sem treino (pet/NPC)</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>razão com treino (pet/NPC)</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>razão de hoje sem treino (poder)</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>razão de hoje com treino (poder)</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>taxa esperada sem treino</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>taxa esperada com treino</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Brutamontes (Gazimon)</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>H3</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>H3*(1+C18*8)</f>
+        <v/>
+      </c>
+      <c r="D25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="G25" s="16">
+        <f>H3*D25</f>
+        <v/>
+      </c>
+      <c r="H25" s="12">
+        <f>B25/G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="12">
+        <f>C25/G25</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>60*0.6/(96*0.6)</f>
+        <v/>
+      </c>
+      <c r="K25" s="12">
+        <f>(60+3.0*8)*0.6/(96*0.6)</f>
+        <v/>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sentinela (Tortomon)</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>H4</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>H4*(1+C18*22)</f>
+        <v/>
+      </c>
+      <c r="D26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="G26" s="16">
+        <f>H4*D26</f>
+        <v/>
+      </c>
+      <c r="H26" s="12">
+        <f>B26/G26</f>
+        <v/>
+      </c>
+      <c r="I26" s="12">
+        <f>C26/G26</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>60*0.8/(72*1.0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>(60+3.0*22)*0.8/(72*1.0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Carcereiro</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>H4</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>H4*(1+C18*22)</f>
+        <v/>
+      </c>
+      <c r="D27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="G27" s="16">
+        <f>H4*D27</f>
+        <v/>
+      </c>
+      <c r="H27" s="12">
+        <f>B27/G27</f>
+        <v/>
+      </c>
+      <c r="I27" s="12">
+        <f>C27/G27</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>60*0.8/(90*1.0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="12">
+        <f>(60+3.0*22)*0.8/(90*1.0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Porteiro</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>H4</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>H4*(1+C18*22)</f>
+        <v/>
+      </c>
+      <c r="D28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="G28" s="16">
+        <f>H4*D28</f>
+        <v/>
+      </c>
+      <c r="H28" s="12">
+        <f>B28/G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="12">
+        <f>C28/G28</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>60*0.8/(90*1.0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>(60+3.0*22)*0.8/(90*1.0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Soberano</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>H5*(1+C18*36)</f>
+        <v/>
+      </c>
+      <c r="D29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSTO</t>
+        </is>
+      </c>
+      <c r="G29" s="16">
+        <f>H5*D29</f>
+        <v/>
+      </c>
+      <c r="H29" s="12">
+        <f>B29/G29</f>
+        <v/>
+      </c>
+      <c r="I29" s="12">
+        <f>C29/G29</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>60*1.0/(110*1.0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="12">
+        <f>(60+3.0*36)*1.0/(110*1.0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>SEM FONTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>leitura</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>com os fatores propostos a razão pet/NPC fica abaixo de 1,0 sem treino e acima com o treino típico em todos os portões (Brutamontes (Gazimon) 0,87 → 1,08; Sentinela (Tortomon) 0,83 → 1,38; Carcereiro 0,77 → 1,28; Porteiro 0,77 → 1,28; Soberano 0,62 → 1,30). Os NPCs da Torre deixam de ter tamanho de adulto: passam à escala do Champion. A taxa esperada só existe depois de rodar (Parte C: calibrar_progressao nas sementes de calibração). As razões de hoje usam o modelo de poder da aba jornada (contas sobre os valores do config.py, visíveis na fórmula).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>E4 redefinido (B2.6, PROPOSTO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>hoje</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>proposta</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>o que mede</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>adulto × adolescente da mesma linha, mesma espécie e caráter, sem treino</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>o treino fecha parte da distância entre estágios: adulto SEM treino × adolescente com o treino MÁXIMO do estágio (22 pontos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>taxa do adulto em [0,60, 0,85]</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>taxa do adulto em [0,60, 0,85] com o adolescente treinado; e adulto sem treino × adolescente sem treino ≥ 0,90 (o 'stat check' é de propósito)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>por quê</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>com escala de franquia o adulto sem treino esmaga o adolescente sem treino (E_adulto/E_adol = 2,5)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>a pergunta vira 'o treino do estágio anterior compensa um pouco a evolução?' (princípio 7: treinar cedo rende)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>resultado de hoje</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>duelista 0,78, emboscador 0,74, espelho 0,62, furioso 0,94, muralha 1,00, sentinela 1,00, tita 0,99, vigia 1,00</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>SEM FONTE até a Parte C (bateria V21C com a escala ligada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Constantes absolutas do combate (B2.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>constante</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>como tornar relativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>dano do golpe rápido</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV2.dano_golpe_rapido</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV2.dano_golpe_rapido</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>vira relativo: × E_A / E_B (unidades de quem recebe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>dano do disparo</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV2.dano_disparo</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV2.dano_disparo</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>dano do pesado</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV2.dano_pesado</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV2.dano_pesado</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>dano do parry (V2C)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV2C.dano_parry</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV2C.dano_parry</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>dano da investida</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21.dano_investida</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21.dano_investida</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>dano extra do duelista</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21.dano_extra_duelista</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21.dano_extra_duelista</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>dano</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>vida base</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21C.hp_base</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>75</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21C.hp_base</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>vida</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>fica nas unidades próprias; a vida exibida é × E (não entra na luta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>vida por vigor</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21C.hp_por_vigor</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21C.hp_por_vigor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>vida</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>multiplicador de estágio (0,4 / 0,6 / 0,8 / 1,0) na vida e no guts</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCatalogo.mult_estagio</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCatalogo.mult_estagio</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>vida e guts</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>sai da campanha: a razão E_A/E_B faz o papel dele na vida; no guts, decidir se fica (proposta: fica, é ritmo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>regeneração de guts por turno (4 + 0,4 × recuperação)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21.regen_base</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21.regen_base</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>guts</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>fica absoluta (ritmo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>custos de guts (golpe 10, pesado 15, disparo e esquiva 20)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV2.custo_*</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV2.custo_*</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>guts</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>guts não precisa escalar: é recurso de ritmo, não magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>guts máximo, inicial, regen, carregar +25, defender +5</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21 / V2</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>25</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21 / V2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>guts</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>idem (fica absoluto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>limiares de guts nas condições (20, 40, 60)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV2.limiares_guts</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV2.limiares_guts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>guts</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>multiplicadores de força/mira/guarda (0,7 + 0,03 × stat)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ConfigCombateV21.mult_base / mult_por_ponto</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>digilab/config.py &gt; ConfigCombateV21.mult_base / mult_por_ponto</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>dependem do stat de catálogo, que NÃO escala (o perfil fica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>frações de vida nas condições (25/50/75%)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>ConfigCombateV2.fracoes_hp</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C55" t="n">
         <v>0.25</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>digilab/config.py &gt; ConfigCombateV2.fracoes_hp</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>fração</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>já relativas</t>
         </is>

--- a/artifacts_progressao/planilha_progressao.xlsx
+++ b/artifacts_progressao/planilha_progressao.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>fe81cab</t>
+          <t>a39b3d8</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T17:43:09-03:00</t>
+          <t>2026-09-28T18:28:33-03:00</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.vida_por_estagio['bebe'] (aprovada na Parte B)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.vida_por_estagio['crianca'] (aprovada na Parte B)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.vida_por_estagio['adolescente'] (aprovada na Parte B)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>proposta (TAREFA B2: ~50 / 200 / 600 / 1500)</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.vida_por_estagio['adulto'] (aprovada na Parte B)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>proposta: 36 pontos → ×2,08 (o treino inteiro da vida pouco mais que dobra a escala)</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.beta_treino (36 pontos → ×2,08)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>proposta: 36 pontos → ×2,08 (o treino inteiro da vida pouco mais que dobra a escala)</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.beta_treino (36 pontos → ×2,08)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>proposta: 36 pontos → ×2,08 (o treino inteiro da vida pouco mais que dobra a escala)</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.beta_treino (36 pontos → ×2,08)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -9196,16 +9196,16 @@
         <v/>
       </c>
       <c r="D25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.fator_npc['tier1_brutamontes'] (calibrado: experiments/configs/escala/calibracao.json)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="G25" s="16">
@@ -9228,26 +9228,30 @@
         <f>(60+3.0*8)*0.6/(96*0.6)</f>
         <v/>
       </c>
-      <c r="L25" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0.2213</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier1_brutamontes.sem (sementes de validação)</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t>ARTEFATO</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9688</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier1_brutamontes.com</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
+          <t>ARTEFATO</t>
         </is>
       </c>
     </row>
@@ -9266,16 +9270,16 @@
         <v/>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.fator_npc['tier2_sentinela'] (calibrado: experiments/configs/escala/calibracao.json)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="G26" s="16">
@@ -9298,26 +9302,30 @@
         <f>(60+3.0*22)*0.8/(72*1.0)</f>
         <v/>
       </c>
-      <c r="L26" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier2_sentinela.sem (sementes de validação)</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
+          <t>ARTEFATO</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier2_sentinela.com</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
+          <t>ARTEFATO</t>
         </is>
       </c>
     </row>
@@ -9336,16 +9344,16 @@
         <v/>
       </c>
       <c r="D27" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.fator_npc['tier2_carcereiro'] (calibrado: experiments/configs/escala/calibracao.json)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="G27" s="16">
@@ -9368,26 +9376,30 @@
         <f>(60+3.0*22)*0.8/(90*1.0)</f>
         <v/>
       </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier2_carcereiro.sem (sementes de validação)</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr"/>
+          <t>ARTEFATO</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8413</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier2_carcereiro.com</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
+          <t>ARTEFATO</t>
         </is>
       </c>
     </row>
@@ -9406,16 +9418,16 @@
         <v/>
       </c>
       <c r="D28" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.fator_npc['tier2_porteiro'] (calibrado: experiments/configs/escala/calibracao.json)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="G28" s="16">
@@ -9438,26 +9450,30 @@
         <f>(60+3.0*22)*0.8/(90*1.0)</f>
         <v/>
       </c>
-      <c r="L28" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0.1969</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier2_porteiro.sem (sementes de validação)</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr"/>
+          <t>ARTEFATO</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8938</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier2_porteiro.com</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
+          <t>ARTEFATO</t>
         </is>
       </c>
     </row>
@@ -9476,16 +9492,16 @@
         <v/>
       </c>
       <c r="D29" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>proposta: NPC na escala do estágio SUGERIDO para ele, um pouco acima do pet sem treino; calibrar na Parte C</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>PROPOSTO</t>
+          <t>digilab/config.py &gt; ConfigEscala.fator_npc['tier3_soberano'] (calibrado: experiments/configs/escala/calibracao.json)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="G29" s="16">
@@ -9508,26 +9524,30 @@
         <f>(60+3.0*36)*1.0/(110*1.0)</f>
         <v/>
       </c>
-      <c r="L29" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier3_soberano.sem (sementes de validação)</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>SEM FONTE</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
+          <t>ARTEFATO</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>experiments/configs/escala/validacao.json &gt; resultado.tier3_soberano.com</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>SEM FONTE</t>
+          <t>ARTEFATO</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9559,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>com os fatores propostos a razão pet/NPC fica abaixo de 1,0 sem treino e acima com o treino típico em todos os portões (Brutamontes (Gazimon) 0,87 → 1,08; Sentinela (Tortomon) 0,83 → 1,38; Carcereiro 0,77 → 1,28; Porteiro 0,77 → 1,28; Soberano 0,62 → 1,30). Os NPCs da Torre deixam de ter tamanho de adulto: passam à escala do Champion. A taxa esperada só existe depois de rodar (Parte C: calibrar_progressao nas sementes de calibração). As razões de hoje usam o modelo de poder da aba jornada (contas sobre os valores do config.py, visíveis na fórmula).</t>
+          <t>com os fatores propostos a razão pet/NPC fica abaixo de 1,0 sem treino e acima com o treino típico em todos os portões (Brutamontes (Gazimon) 0,91 → 1,13; Sentinela (Tortomon) 0,62 → 1,04; Carcereiro 0,67 → 1,11; Porteiro 0,91 → 1,51; Soberano 0,83 → 1,73). Os NPCs da Torre deixam de ter tamanho de adulto: passam à escala do Champion. As taxas vêm da validação da Parte C (experiments/calibrar_escala.py --validar); a Sentinela não fecha com nenhum fator (estilo tartaruga). As razões de hoje usam o modelo de poder da aba jornada (contas sobre os valores do config.py, visíveis na fórmula).</t>
         </is>
       </c>
     </row>

--- a/artifacts_progressao/planilha_progressao.xlsx
+++ b/artifacts_progressao/planilha_progressao.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>a39b3d8</t>
+          <t>8414ab6</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T18:28:33-03:00</t>
+          <t>2026-09-28T18:29:32-03:00</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>E4 redefinido (B2.6, PROPOSTO)</t>
+          <t>E4 redefinido (B2.6; definição final do Matheus depois da Parte C)</t>
         </is>
       </c>
     </row>
@@ -9578,12 +9578,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>hoje</t>
+          <t>antes da escala</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>proposta</t>
+          <t>na escala</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>o treino fecha parte da distância entre estágios: adulto SEM treino × adolescente com o treino MÁXIMO do estágio (22 pontos)</t>
+          <t>a evolução sempre importa: adulto SEM treino × adolescente sem treino e com o treino máximo do estágio (+22)</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>taxa do adulto em [0,60, 0,85] com o adolescente treinado; e adulto sem treino × adolescente sem treino ≥ 0,90 (o 'stat check' é de propósito)</t>
+          <t>taxa do adulto ≥ 0,60 nos dois casos, sem teto (esmagar é de propósito na escala)</t>
         </is>
       </c>
     </row>
@@ -9629,19 +9629,19 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>com escala de franquia o adulto sem treino esmaga o adolescente sem treino (E_adulto/E_adol = 2,5)</t>
+          <t>com escala de franquia o adulto sem treino esmaga o adolescente (E_adulto/E_Champion = 2,5)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>a pergunta vira 'o treino do estágio anterior compensa um pouco a evolução?' (princípio 7: treinar cedo rende)</t>
+          <t>a Parte B propunha E4' (treino compensa: faixa [0,60, 0,85]) e E4'' (≥ 0,90); os dois reprovaram e o Matheus redefiniu</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>resultado de hoje</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SEM FONTE até a Parte C (bateria V21C com a escala ligada)</t>
+          <t>OK — adulto sem treino x adolescente (sem treino e com +22): abaixo de 0.6: nenhum; menor 0.836</t>
         </is>
       </c>
     </row>
